--- a/public/excel/product/Giá thép ống đen.xlsx
+++ b/public/excel/product/Giá thép ống đen.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="83">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép ống đen 88.3 x 5.0 x 6m</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép ống đen 88.3 x 5.2 x 6m</t>
@@ -522,7 +528,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -583,7 +591,7 @@
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>6</v>
@@ -595,21 +603,23 @@
         <v>16.364</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -670,7 +680,7 @@
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>6</v>
@@ -682,21 +692,23 @@
         <v>16.364</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -757,7 +769,7 @@
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>6</v>
@@ -769,21 +781,23 @@
         <v>16.364</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -844,7 +858,7 @@
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>6</v>
@@ -856,21 +870,23 @@
         <v>16.364</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -931,7 +947,7 @@
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>6</v>
@@ -952,12 +968,14 @@
         <v>505.765</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1018,7 +1036,7 @@
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>6</v>
@@ -1039,12 +1057,14 @@
         <v>561.017</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1105,7 +1125,7 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>6</v>
@@ -1126,12 +1146,14 @@
         <v>643.299</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1192,7 +1214,7 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>6</v>
@@ -1213,12 +1235,14 @@
         <v>698.041</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1279,7 +1303,7 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>6</v>
@@ -1300,12 +1324,14 @@
         <v>779.643</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -1366,7 +1392,7 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>6</v>
@@ -1387,12 +1413,14 @@
         <v>833.875</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -1453,7 +1481,7 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>6</v>
@@ -1474,12 +1502,14 @@
         <v>887.936</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1540,7 +1570,7 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>6</v>
@@ -1561,12 +1591,14 @@
         <v>968.518</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -1627,7 +1659,7 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>6</v>
@@ -1645,15 +1677,17 @@
         <v>17.001</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1714,7 +1748,7 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>6</v>
@@ -1726,21 +1760,23 @@
         <v>15.455</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>17.001</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1801,7 +1837,7 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>6</v>
@@ -1822,12 +1858,14 @@
         <v>888.446</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1888,7 +1926,7 @@
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>6</v>
@@ -1906,15 +1944,17 @@
         <v>17.001</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -1975,7 +2015,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>6</v>
@@ -1987,21 +2027,23 @@
         <v>15.455</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>17.001</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2062,7 +2104,7 @@
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>6</v>
@@ -2074,21 +2116,23 @@
         <v>15.455</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>17.001</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2149,7 +2193,7 @@
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>6</v>
@@ -2161,21 +2205,23 @@
         <v>16.955</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>18.651</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2236,7 +2282,7 @@
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>6</v>
@@ -2248,21 +2294,23 @@
         <v>16.955</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>18.651</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2323,7 +2371,7 @@
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>6</v>
@@ -2335,21 +2383,23 @@
         <v>16.955</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>18.651</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -2410,7 +2460,7 @@
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>6</v>
@@ -2422,21 +2472,23 @@
         <v>16.955</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>18.651</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -2497,7 +2549,7 @@
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>6</v>
@@ -2509,21 +2561,23 @@
         <v>16.682</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>18.35</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2584,7 +2638,7 @@
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>6</v>
@@ -2596,21 +2650,23 @@
         <v>16.682</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>18.35</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2671,7 +2727,7 @@
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>6</v>
@@ -2683,21 +2739,23 @@
         <v>16.682</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>18.35</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J26" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2758,7 +2816,7 @@
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>6</v>
@@ -2770,21 +2828,23 @@
         <v>16.682</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>18.35</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J27" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2845,7 +2905,7 @@
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>6</v>
@@ -2857,21 +2917,23 @@
         <v>17.409</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>19.15</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2932,7 +2994,7 @@
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>6</v>
@@ -2944,21 +3006,23 @@
         <v>17.409</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>19.15</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -3019,7 +3083,7 @@
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>6</v>
@@ -3031,21 +3095,23 @@
         <v>17.409</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>19.15</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -3106,7 +3172,7 @@
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>6</v>
@@ -3118,21 +3184,23 @@
         <v>17.409</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>19.15</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
